--- a/clients/Lawrence_Client1_Kenya.xlsx
+++ b/clients/Lawrence_Client1_Kenya.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c1e174b27b94807/Desktop/PortfolioTracker/clients/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_09C9AF2A7231FE99B5EDE0B00038F1AF6A203683" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6966FE22-887F-4E49-94EB-4D95B0AC7D22}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_09C9AF2A7231FE99B5EDE0B00038F1AF6A203683" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBA75CCE-9709-4313-9CBD-B56D9C4D487F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,18 @@
     <sheet name="Dividend Tracking" sheetId="3" r:id="rId3"/>
     <sheet name="Dashboard1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -470,10 +481,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -482,14 +500,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1032,16 +1043,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>25.766313243034666</c:v>
+                  <c:v>27.324233250121559</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.529521070019353</c:v>
+                  <c:v>17.854820150320688</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24.83348586880745</c:v>
+                  <c:v>23.75795897143372</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30.870679818138534</c:v>
+                  <c:v>31.062987628124045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1296,16 +1307,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>45.776377322739776</c:v>
+                  <c:v>47.207863220290001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.948079371393607</c:v>
+                  <c:v>25.59538256420791</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.670875071708968</c:v>
+                  <c:v>13.361412288903225</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.604668234157643</c:v>
+                  <c:v>13.835341926598868</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1755,25 +1766,25 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>11.794884772290617</c:v>
+                  <c:v>12.899186658710384</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.4821434811086291</c:v>
+                  <c:v>8.4288790747921674</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.367870193694561</c:v>
+                  <c:v>11.215624775167047</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.131478875645975</c:v>
+                  <c:v>14.664172711620404</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.670875071708968</c:v>
+                  <c:v>13.361412288903225</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.948079371393607</c:v>
+                  <c:v>25.59538256420791</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.604668234157643</c:v>
+                  <c:v>13.835341926598868</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2265,21 +2276,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -2322,11 +2333,11 @@
       </c>
       <c r="D3" s="27">
         <f>D19</f>
-        <v>45.776377322739776</v>
+        <v>47.207863220290001</v>
       </c>
       <c r="E3" s="27">
         <f>D3-C3</f>
-        <v>-4.2236226772602237</v>
+        <v>-2.792136779709999</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
@@ -2347,11 +2358,11 @@
       </c>
       <c r="D4" s="27">
         <f>D20</f>
-        <v>20.948079371393607</v>
+        <v>25.59538256420791</v>
       </c>
       <c r="E4" s="27">
         <f>D4-C4</f>
-        <v>-9.0519206286063927</v>
+        <v>-4.4046174357920904</v>
       </c>
       <c r="F4" s="33"/>
       <c r="G4" s="33"/>
@@ -2380,11 +2391,11 @@
       </c>
       <c r="D5" s="27">
         <f>D21</f>
-        <v>12.670875071708968</v>
+        <v>13.361412288903225</v>
       </c>
       <c r="E5" s="27">
         <f>D5-C5</f>
-        <v>-2.3291249282910318</v>
+        <v>-1.6385877110967755</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
@@ -2405,11 +2416,11 @@
       </c>
       <c r="D6" s="27">
         <f>D22</f>
-        <v>20.604668234157643</v>
+        <v>13.835341926598868</v>
       </c>
       <c r="E6" s="27">
         <f>D6-C6</f>
-        <v>15.604668234157643</v>
+        <v>8.8353419265988684</v>
       </c>
       <c r="F6" s="33"/>
       <c r="G6" s="33"/>
@@ -2476,11 +2487,11 @@
       </c>
       <c r="D9" s="27">
         <f>C29</f>
-        <v>25.766313243034666</v>
+        <v>27.324233250121559</v>
       </c>
       <c r="E9" s="27">
         <f>D9-C9</f>
-        <v>-4.2336867569653336</v>
+        <v>-2.6757667498784414</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
@@ -2501,11 +2512,11 @@
       </c>
       <c r="D10" s="27">
         <f>C30</f>
-        <v>18.529521070019353</v>
+        <v>17.854820150320688</v>
       </c>
       <c r="E10" s="27">
         <f>D10-C10</f>
-        <v>-1.4704789299806471</v>
+        <v>-2.1451798496793124</v>
       </c>
       <c r="F10" s="33"/>
       <c r="G10" s="33"/>
@@ -2534,11 +2545,11 @@
       </c>
       <c r="D11" s="27">
         <f>C31</f>
-        <v>24.83348586880745</v>
+        <v>23.75795897143372</v>
       </c>
       <c r="E11" s="27">
         <f>D11-C11</f>
-        <v>4.8334858688074505</v>
+        <v>3.7579589714337196</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
@@ -2559,11 +2570,11 @@
       </c>
       <c r="D12" s="27">
         <f>C32</f>
-        <v>30.870679818138534</v>
+        <v>31.062987628124045</v>
       </c>
       <c r="E12" s="27">
         <f>D12-C12</f>
-        <v>0.87067981813853379</v>
+        <v>1.0629876281240449</v>
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="33"/>
@@ -2659,7 +2670,7 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="1:21" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="54"/>
@@ -2713,11 +2724,11 @@
       </c>
       <c r="C19" s="27">
         <f>Holdings!C43</f>
-        <v>6664952.3499999996</v>
+        <v>6824242.3599999994</v>
       </c>
       <c r="D19" s="27">
         <f>SUM(Holdings!D35:'Holdings'!D38)</f>
-        <v>45.776377322739776</v>
+        <v>47.207863220290001</v>
       </c>
       <c r="E19" s="42">
         <v>9.5000000000000001E-2</v>
@@ -2738,11 +2749,11 @@
       </c>
       <c r="C20" s="40">
         <f>Holdings!C40</f>
-        <v>3050000</v>
+        <v>3700000</v>
       </c>
       <c r="D20" s="40">
         <f>Holdings!D40</f>
-        <v>20.948079371393607</v>
+        <v>25.59538256420791</v>
       </c>
       <c r="E20" s="41">
         <v>0.14499999999999999</v>
@@ -2763,11 +2774,11 @@
       </c>
       <c r="C21" s="27">
         <f>Holdings!C39</f>
-        <v>1844855</v>
+        <v>1931490</v>
       </c>
       <c r="D21" s="27">
         <f>Holdings!D39</f>
-        <v>12.670875071708968</v>
+        <v>13.361412288903225</v>
       </c>
       <c r="E21" s="42">
         <v>1.0500000000000001E-2</v>
@@ -2788,11 +2799,11 @@
       </c>
       <c r="C22" s="40">
         <f>Holdings!C41</f>
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="D22" s="40">
         <f>Holdings!D41</f>
-        <v>20.604668234157643</v>
+        <v>13.835341926598868</v>
       </c>
       <c r="E22" s="41">
         <v>0.105</v>
@@ -2907,7 +2918,7 @@
       </c>
       <c r="C29" s="40">
         <f>Holdings!C35/C19*100</f>
-        <v>25.766313243034666</v>
+        <v>27.324233250121559</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="37"/>
@@ -2927,7 +2938,7 @@
       </c>
       <c r="C30" s="27">
         <f>Holdings!C36/C19*100</f>
-        <v>18.529521070019353</v>
+        <v>17.854820150320688</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
@@ -2947,7 +2958,7 @@
       </c>
       <c r="C31" s="40">
         <f>Holdings!C37/C19*100</f>
-        <v>24.83348586880745</v>
+        <v>23.75795897143372</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="37"/>
@@ -2967,7 +2978,7 @@
       </c>
       <c r="C32" s="27">
         <f>Holdings!C38/C19*100</f>
-        <v>30.870679818138534</v>
+        <v>31.062987628124045</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
@@ -3239,13 +3250,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="57" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
+      <c r="C1" s="58"/>
       <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+      <c r="E1" s="58"/>
       <c r="F1" s="54"/>
       <c r="G1" s="54"/>
       <c r="H1" s="54"/>
@@ -3295,23 +3306,23 @@
       <c r="O2" s="52"/>
     </row>
     <row r="3" spans="1:15" s="6" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
     </row>
     <row r="4" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
@@ -3324,11 +3335,11 @@
         <v>5</v>
       </c>
       <c r="D4" s="9">
-        <v>16500</v>
+        <v>15909</v>
       </c>
       <c r="E4" s="22">
         <f>H4/(SUM(H4:H7))*100</f>
-        <v>30.8417949557812</v>
+        <v>27.387064716318193</v>
       </c>
       <c r="F4" s="9">
         <v>32.1</v>
@@ -3339,15 +3350,15 @@
       </c>
       <c r="H4" s="9">
         <f>D4*F4</f>
-        <v>529650</v>
+        <v>510678.9</v>
       </c>
       <c r="I4" s="10">
         <f>D4*G4</f>
-        <v>562650</v>
+        <v>542496.9</v>
       </c>
       <c r="J4" s="10">
         <f>I4-H4</f>
-        <v>33000</v>
+        <v>31818</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
@@ -3366,11 +3377,11 @@
         <v>5</v>
       </c>
       <c r="D5" s="11">
-        <v>7500</v>
+        <v>7733</v>
       </c>
       <c r="E5" s="22">
         <f>H5/(SUM(H4:H7))*100</f>
-        <v>32.427120864723221</v>
+        <v>30.792293807827537</v>
       </c>
       <c r="F5" s="11">
         <v>74.25</v>
@@ -3381,15 +3392,15 @@
       </c>
       <c r="H5" s="11">
         <f>D5*F5</f>
-        <v>556875</v>
+        <v>574175.25</v>
       </c>
       <c r="I5" s="10">
         <f>D5*G5</f>
-        <v>571875</v>
+        <v>589641.25</v>
       </c>
       <c r="J5" s="10">
         <f>I5-H5</f>
-        <v>15000</v>
+        <v>15466</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
@@ -3408,11 +3419,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="9">
-        <v>9450</v>
+        <v>9522</v>
       </c>
       <c r="E6" s="22">
         <f>H6/(SUM(H4:H7))*100</f>
-        <v>36.731084179495575</v>
+        <v>34.08607701976954</v>
       </c>
       <c r="F6" s="9">
         <v>66.75</v>
@@ -3423,15 +3434,15 @@
       </c>
       <c r="H6" s="9">
         <f>D6*F6</f>
-        <v>630787.5</v>
+        <v>635593.5</v>
       </c>
       <c r="I6" s="10">
         <f>D6*G6</f>
-        <v>649687.5</v>
+        <v>654637.5</v>
       </c>
       <c r="J6" s="10">
         <f>I6-H6</f>
-        <v>18900</v>
+        <v>19044</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
@@ -3450,11 +3461,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="11">
-        <v>0</v>
+        <v>1653</v>
       </c>
       <c r="E7" s="22">
         <f>H7/(SUM(H4:H7))*100</f>
-        <v>0</v>
+        <v>7.7345644560847413</v>
       </c>
       <c r="F7" s="11">
         <v>87.25</v>
@@ -3465,15 +3476,15 @@
       </c>
       <c r="H7" s="11">
         <f>D7*F7</f>
-        <v>0</v>
+        <v>144224.25</v>
       </c>
       <c r="I7" s="10">
         <f>D7*G7</f>
-        <v>0</v>
+        <v>147530.25</v>
       </c>
       <c r="J7" s="10">
         <f>I7-H7</f>
-        <v>0</v>
+        <v>3306</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
@@ -3499,23 +3510,23 @@
       <c r="O8" s="10"/>
     </row>
     <row r="9" spans="1:15" s="6" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="57"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="60"/>
     </row>
     <row r="10" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -3528,7 +3539,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="9">
-        <v>40425</v>
+        <v>39884</v>
       </c>
       <c r="E10" s="22">
         <f>H10/H10*100</f>
@@ -3543,15 +3554,15 @@
       </c>
       <c r="H10" s="9">
         <f>D10*F10</f>
-        <v>1234983.75</v>
+        <v>1218456.2</v>
       </c>
       <c r="I10" s="10">
         <f>D10*G10</f>
-        <v>1315833.75</v>
+        <v>1298224.2</v>
       </c>
       <c r="J10" s="10">
         <f>I10-H10</f>
-        <v>80850</v>
+        <v>79768</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
@@ -3577,23 +3588,23 @@
       <c r="O11" s="13"/>
     </row>
     <row r="12" spans="1:15" s="6" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="57"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="60"/>
     </row>
     <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
@@ -3606,11 +3617,11 @@
         <v>3.33</v>
       </c>
       <c r="D13" s="12">
-        <v>2358</v>
+        <v>2253</v>
       </c>
       <c r="E13" s="22">
         <f>H13/(SUM(H13:H15))*100</f>
-        <v>51.287504380294116</v>
+        <v>50.02650032779237</v>
       </c>
       <c r="F13" s="12">
         <v>360</v>
@@ -3621,15 +3632,15 @@
       </c>
       <c r="H13" s="12">
         <f>D13*F13</f>
-        <v>848880</v>
+        <v>811080</v>
       </c>
       <c r="I13" s="10">
         <f>D13*G13</f>
-        <v>853596</v>
+        <v>815586</v>
       </c>
       <c r="J13" s="10">
         <f>I13-H13</f>
-        <v>4716</v>
+        <v>4506</v>
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
@@ -3648,11 +3659,11 @@
         <v>3.33</v>
       </c>
       <c r="D14" s="9">
-        <v>99500</v>
+        <v>104150</v>
       </c>
       <c r="E14" s="22">
         <f>H14/(SUM(H13:H15))*100</f>
-        <v>25.188503691530627</v>
+        <v>26.915950878205386</v>
       </c>
       <c r="F14" s="9">
         <v>4.1900000000000004</v>
@@ -3663,15 +3674,15 @@
       </c>
       <c r="H14" s="9">
         <f>D14*F14</f>
-        <v>416905.00000000006</v>
+        <v>436388.50000000006</v>
       </c>
       <c r="I14" s="10">
         <f>D14*G14</f>
-        <v>615905</v>
+        <v>644688.5</v>
       </c>
       <c r="J14" s="10">
         <f>I14-H14</f>
-        <v>198999.99999999994</v>
+        <v>208299.99999999994</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
@@ -3690,11 +3701,11 @@
         <v>3.34</v>
       </c>
       <c r="D15" s="12">
-        <v>30300</v>
+        <v>29092</v>
       </c>
       <c r="E15" s="22">
         <f>H15/(SUM(H13:H15))*100</f>
-        <v>23.52399192817526</v>
+        <v>23.057548794002251</v>
       </c>
       <c r="F15" s="12">
         <v>12.85</v>
@@ -3705,15 +3716,15 @@
       </c>
       <c r="H15" s="12">
         <f>D15*F15</f>
-        <v>389355</v>
+        <v>373832.2</v>
       </c>
       <c r="I15" s="10">
         <f>D15*G15</f>
-        <v>449955</v>
+        <v>432016.2</v>
       </c>
       <c r="J15" s="10">
         <f>I15-H15</f>
-        <v>60600</v>
+        <v>58184</v>
       </c>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
@@ -3739,23 +3750,23 @@
       <c r="O16" s="14"/>
     </row>
     <row r="17" spans="1:15" s="6" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="60"/>
     </row>
     <row r="18" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
@@ -3768,11 +3779,11 @@
         <v>3.33</v>
       </c>
       <c r="D18" s="9">
-        <v>45970</v>
+        <v>44757</v>
       </c>
       <c r="E18" s="22">
         <f>H18/(SUM(H18:H20))*100</f>
-        <v>20.510391145906461</v>
+        <v>19.382330019626821</v>
       </c>
       <c r="F18" s="9">
         <v>9.18</v>
@@ -3783,15 +3794,15 @@
       </c>
       <c r="H18" s="9">
         <f>D18*F18</f>
-        <v>422004.6</v>
+        <v>410869.26</v>
       </c>
       <c r="I18" s="10">
         <f>D18*G18</f>
-        <v>513944.6</v>
+        <v>500383.26</v>
       </c>
       <c r="J18" s="10">
         <f>I18-H18</f>
-        <v>91940</v>
+        <v>89514</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
@@ -3810,11 +3821,11 @@
         <v>3.33</v>
       </c>
       <c r="D19" s="12">
-        <v>46890</v>
+        <v>49848</v>
       </c>
       <c r="E19" s="22">
         <f>H19/(SUM(H18:H20))*100</f>
-        <v>34.982059192635234</v>
+        <v>36.09594798516148</v>
       </c>
       <c r="F19" s="12">
         <v>15.35</v>
@@ -3825,15 +3836,15 @@
       </c>
       <c r="H19" s="12">
         <f>D19*F19</f>
-        <v>719761.5</v>
+        <v>765166.79999999993</v>
       </c>
       <c r="I19" s="14">
         <f>D19*G19</f>
-        <v>813541.50000000012</v>
+        <v>864862.8</v>
       </c>
       <c r="J19" s="10">
         <f>I19-H19</f>
-        <v>93780.000000000116</v>
+        <v>99696.000000000116</v>
       </c>
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
@@ -3852,11 +3863,11 @@
         <v>3.34</v>
       </c>
       <c r="D20" s="9">
-        <v>16500</v>
+        <v>17005</v>
       </c>
       <c r="E20" s="22">
         <f t="shared" ref="E20" si="0">H20/(SUM(H18:H20))*100</f>
-        <v>44.507549661458299</v>
+        <v>44.521721995211685</v>
       </c>
       <c r="F20" s="9">
         <v>55.5</v>
@@ -3867,15 +3878,15 @@
       </c>
       <c r="H20" s="9">
         <f>D20*F20</f>
-        <v>915750</v>
+        <v>943777.5</v>
       </c>
       <c r="I20" s="10">
         <f>D20*G20</f>
-        <v>948750</v>
+        <v>977787.5</v>
       </c>
       <c r="J20" s="10">
         <f>I20-H20</f>
-        <v>33000</v>
+        <v>34010</v>
       </c>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
@@ -3901,23 +3912,23 @@
       <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" s="6" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="57"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
@@ -3930,11 +3941,11 @@
         <v>10</v>
       </c>
       <c r="D23" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="22">
         <f>H23/(SUM(H23:H24))*100</f>
-        <v>70.791471416452779</v>
+        <v>70.320840387472884</v>
       </c>
       <c r="F23" s="9">
         <v>52240</v>
@@ -3945,15 +3956,15 @@
       </c>
       <c r="H23" s="9">
         <f>D23*F23</f>
-        <v>1306000</v>
+        <v>1358240</v>
       </c>
       <c r="I23" s="10">
         <f>D23*G23</f>
-        <v>1306050</v>
+        <v>1358292</v>
       </c>
       <c r="J23" s="10">
         <f>I23-H23</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
@@ -3972,11 +3983,11 @@
         <v>5</v>
       </c>
       <c r="D24" s="12">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E24" s="22">
         <f>H24/(SUM(H23:H24))*100</f>
-        <v>29.208528583547217</v>
+        <v>29.679159612527116</v>
       </c>
       <c r="F24" s="12">
         <v>11465</v>
@@ -3987,15 +3998,15 @@
       </c>
       <c r="H24" s="12">
         <f>D24*F24</f>
-        <v>538855</v>
+        <v>573250</v>
       </c>
       <c r="I24" s="10">
         <f>D24*G24</f>
-        <v>538949</v>
+        <v>573350</v>
       </c>
       <c r="J24" s="10">
         <f>I24-H24</f>
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
@@ -4021,23 +4032,23 @@
       <c r="O25" s="14"/>
     </row>
     <row r="26" spans="1:15" s="6" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="60"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
@@ -4050,7 +4061,7 @@
         <v>30</v>
       </c>
       <c r="D27" s="9">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E27" s="22">
         <f>D27/D27*100</f>
@@ -4065,7 +4076,7 @@
       </c>
       <c r="H27" s="9">
         <f>D27*F27</f>
-        <v>3050000</v>
+        <v>3700000</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
@@ -4093,23 +4104,23 @@
       <c r="O28" s="10"/>
     </row>
     <row r="29" spans="1:15" s="6" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="57"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="60"/>
+      <c r="M29" s="60"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="60"/>
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
@@ -4122,7 +4133,7 @@
         <v>5</v>
       </c>
       <c r="D30" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="24">
         <f>D30/D30*100</f>
@@ -4137,7 +4148,7 @@
       </c>
       <c r="H30" s="12">
         <f>D30*F30</f>
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
@@ -4182,23 +4193,23 @@
       <c r="O32" s="14"/>
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="59"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="59"/>
-      <c r="J33" s="59"/>
-      <c r="K33" s="59"/>
-      <c r="L33" s="59"/>
-      <c r="M33" s="59"/>
-      <c r="N33" s="59"/>
-      <c r="O33" s="59"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="56"/>
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16"/>
@@ -4211,17 +4222,17 @@
       <c r="D34" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="59"/>
-      <c r="M34" s="59"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
       <c r="N34" s="15"/>
       <c r="O34" s="15"/>
     </row>
@@ -4232,11 +4243,11 @@
       </c>
       <c r="C35" s="25">
         <f>SUM(H4:H7)</f>
-        <v>1717312.5</v>
+        <v>1864671.9</v>
       </c>
       <c r="D35" s="25">
         <f>C35/C45*100</f>
-        <v>11.794884772290617</v>
+        <v>12.899186658710384</v>
       </c>
       <c r="E35" s="25"/>
       <c r="F35" s="18"/>
@@ -4257,11 +4268,11 @@
       </c>
       <c r="C36" s="26">
         <f>H10</f>
-        <v>1234983.75</v>
+        <v>1218456.2</v>
       </c>
       <c r="D36" s="25">
         <f>C36/C45*100</f>
-        <v>8.4821434811086291</v>
+        <v>8.4288790747921674</v>
       </c>
       <c r="E36" s="26"/>
       <c r="F36" s="19"/>
@@ -4282,11 +4293,11 @@
       </c>
       <c r="C37" s="25">
         <f>SUM(H13:H15)</f>
-        <v>1655140</v>
+        <v>1621300.7</v>
       </c>
       <c r="D37" s="25">
         <f>C37/C45*100</f>
-        <v>11.367870193694561</v>
+        <v>11.215624775167047</v>
       </c>
       <c r="E37" s="25"/>
       <c r="F37" s="18"/>
@@ -4307,11 +4318,11 @@
       </c>
       <c r="C38" s="26">
         <f>SUM(H18:H20)</f>
-        <v>2057516.1</v>
+        <v>2119813.56</v>
       </c>
       <c r="D38" s="25">
         <f>C38/C45*100</f>
-        <v>14.131478875645975</v>
+        <v>14.664172711620404</v>
       </c>
       <c r="E38" s="26"/>
       <c r="F38" s="19"/>
@@ -4332,11 +4343,11 @@
       </c>
       <c r="C39" s="25">
         <f>SUM(H23:H24)</f>
-        <v>1844855</v>
+        <v>1931490</v>
       </c>
       <c r="D39" s="25">
         <f>C39/C45*100</f>
-        <v>12.670875071708968</v>
+        <v>13.361412288903225</v>
       </c>
       <c r="E39" s="25"/>
       <c r="F39" s="18"/>
@@ -4357,11 +4368,11 @@
       </c>
       <c r="C40" s="26">
         <f>H27</f>
-        <v>3050000</v>
+        <v>3700000</v>
       </c>
       <c r="D40" s="25">
         <f>C40/C45*100</f>
-        <v>20.948079371393607</v>
+        <v>25.59538256420791</v>
       </c>
       <c r="E40" s="26"/>
       <c r="F40" s="19"/>
@@ -4382,11 +4393,11 @@
       </c>
       <c r="C41" s="25">
         <f>H30</f>
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="D41" s="25">
         <f>C41/C45*100</f>
-        <v>20.604668234157643</v>
+        <v>13.835341926598868</v>
       </c>
       <c r="E41" s="25"/>
       <c r="F41" s="18"/>
@@ -4424,7 +4435,7 @@
       </c>
       <c r="C43" s="36">
         <f>SUM(C35:C38)</f>
-        <v>6664952.3499999996</v>
+        <v>6824242.3599999994</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="25"/>
@@ -4463,7 +4474,7 @@
       </c>
       <c r="C45" s="25">
         <f>SUM(C35:C41)</f>
-        <v>14559807.35</v>
+        <v>14455732.359999999</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="28"/>
@@ -4566,7 +4577,7 @@
       <c r="C2" s="14"/>
       <c r="D2" s="14">
         <f>Holdings!D4</f>
-        <v>16500</v>
+        <v>15909</v>
       </c>
       <c r="E2" s="14"/>
     </row>
@@ -4578,7 +4589,7 @@
       <c r="C3" s="14"/>
       <c r="D3" s="14">
         <f>Holdings!D5</f>
-        <v>7500</v>
+        <v>7733</v>
       </c>
       <c r="E3" s="14"/>
     </row>
@@ -4590,7 +4601,7 @@
       <c r="C4" s="14"/>
       <c r="D4" s="14">
         <f>Holdings!D6</f>
-        <v>9450</v>
+        <v>9522</v>
       </c>
       <c r="E4" s="14"/>
     </row>
@@ -4602,7 +4613,7 @@
       <c r="C5" s="14"/>
       <c r="D5" s="14">
         <f>Holdings!D7</f>
-        <v>0</v>
+        <v>1653</v>
       </c>
       <c r="E5" s="14"/>
     </row>
@@ -4614,7 +4625,7 @@
       <c r="C6" s="14"/>
       <c r="D6" s="14">
         <f>Holdings!D10</f>
-        <v>40425</v>
+        <v>39884</v>
       </c>
       <c r="E6" s="14"/>
     </row>
@@ -4626,7 +4637,7 @@
       <c r="C7" s="14"/>
       <c r="D7" s="14">
         <f>Holdings!D13</f>
-        <v>2358</v>
+        <v>2253</v>
       </c>
       <c r="E7" s="14"/>
     </row>
@@ -4638,7 +4649,7 @@
       <c r="C8" s="14"/>
       <c r="D8" s="14">
         <f>Holdings!D14</f>
-        <v>99500</v>
+        <v>104150</v>
       </c>
       <c r="E8" s="14"/>
     </row>
@@ -4650,7 +4661,7 @@
       <c r="C9" s="14"/>
       <c r="D9" s="14">
         <f>Holdings!D15</f>
-        <v>30300</v>
+        <v>29092</v>
       </c>
       <c r="E9" s="14"/>
     </row>
@@ -4662,7 +4673,7 @@
       <c r="C10" s="14"/>
       <c r="D10" s="14">
         <f>Holdings!D18</f>
-        <v>45970</v>
+        <v>44757</v>
       </c>
       <c r="E10" s="14"/>
     </row>
@@ -4674,7 +4685,7 @@
       <c r="C11" s="14"/>
       <c r="D11" s="14">
         <f>Holdings!D19</f>
-        <v>46890</v>
+        <v>49848</v>
       </c>
       <c r="E11" s="14"/>
     </row>
@@ -4686,7 +4697,7 @@
       <c r="C12" s="14"/>
       <c r="D12" s="14">
         <f>Holdings!D20</f>
-        <v>16500</v>
+        <v>17005</v>
       </c>
       <c r="E12" s="14"/>
     </row>
@@ -4698,7 +4709,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14">
         <f>Holdings!D23</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="14"/>
     </row>
@@ -4710,7 +4721,7 @@
       <c r="C14" s="14"/>
       <c r="D14" s="14">
         <f>Holdings!D24</f>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="14"/>
     </row>
